--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,9 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>heroImages</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
@@ -43,6 +46,9 @@
     <t>["hero","feedback"]</t>
   </si>
   <si>
+    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/9b48a55da5974906b6d65a89fb9d5d06/kura-tawhiti-hero.jpg -&gt; /content/dam/nzdoc/heros/kura-tawhiti-hero.jpg</t>
+  </si>
+  <si>
     <t>index</t>
   </si>
   <si>
@@ -52,7 +58,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-28T02:02:52.120Z</t>
+    <t>2026-09-28T02:13:43.592Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
@@ -447,19 +453,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="33" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="33" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,35 +491,41 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,9 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>contentListMore</t>
+  </si>
+  <si>
     <t>heroImages</t>
   </si>
   <si>
@@ -43,7 +46,10 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero","feedback"]</t>
+    <t>["hero","cards","columns","feedback"]</t>
+  </si>
+  <si>
+    <t>Featured: https://www.doc.govt.nz/footer-links/new-on-the-site/; Media releases: https://www.doc.govt.nz/news/media-releases/2026-media-releases/</t>
   </si>
   <si>
     <t>https://www.doc.govt.nz/thumbs/hero/contentassets/9b48a55da5974906b6d65a89fb9d5d06/kura-tawhiti-hero.jpg -&gt; /content/dam/nzdoc/heros/kura-tawhiti-hero.jpg</t>
@@ -58,7 +64,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-28T02:13:43.592Z</t>
+    <t>2026-09-28T02:52:36.786Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
@@ -453,20 +459,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="33" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="3" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="33" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,38 +500,44 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="71">
   <si>
     <t>_reportFile</t>
   </si>
@@ -22,6 +22,9 @@
     <t>contentListMore</t>
   </si>
   <si>
+    <t>damImages</t>
+  </si>
+  <si>
     <t>heroImages</t>
   </si>
   <si>
@@ -52,7 +55,10 @@
     <t>Featured: https://www.doc.govt.nz/footer-links/new-on-the-site/; Media releases: https://www.doc.govt.nz/news/media-releases/2026-media-releases/</t>
   </si>
   <si>
-    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/9b48a55da5974906b6d65a89fb9d5d06/kura-tawhiti-hero.jpg -&gt; /content/dam/nzdoc/heros/kura-tawhiti-hero.jpg</t>
+    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/9b48a55da5974906b6d65a89fb9d5d06/kura-tawhiti-hero.jpg -&gt; /content/dam/nzdoc/heros/kura-tawhiti-hero.jpg; https://www.doc.govt.nz/thumbs/gallery/contentassets/a8cf8502518043808b916575ca1bb512/denniston-hero.jpg -&gt; /content/dam/nzdoc/heros/denniston-hero.jpg; https://i0.wp.com/blog.doc.govt.nz/wp-content/uploads/2026/09/black-robin-invertebrate-leon-everett-1-e1788825954346.jpg?w=200 -&gt; /content/dam/nzdoc/blogs/2026/black-robin-invertebrate-leon-everett-1-e1788825954346.jpg</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>index</t>
@@ -64,13 +70,160 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-28T02:52:36.786Z</t>
+    <t>2026-09-28T03:19:20.863Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
   </si>
   <si>
     <t>https://www.doc.govt.nz/</t>
+  </si>
+  <si>
+    <t>news/issues/bird-flu-updates.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","hero"]</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/thumbs/hero/globalassets/images/nature/native-animals/birds/brown-skua/brown-skua-1920.jpg -&gt; /content/dam/nzdoc/heros/brown-skua-1920.jpg</t>
+  </si>
+  <si>
+    <t>news/issues/bird-flu-updates</t>
+  </si>
+  <si>
+    <t>article-hero</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:05:43.233Z</t>
+  </si>
+  <si>
+    <t>EMA: Bird flu updates: Issues</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/news/issues/bird-flu-updates/</t>
+  </si>
+  <si>
+    <t>about-us/our-role/managing-conservation/conservation-amendment-bill.report.json</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/59e382809add463ea8fa893707db334d/whakatane-hero.jpg -&gt; /content/dam/nzdoc/heros/whakatane-hero.jpg</t>
+  </si>
+  <si>
+    <t>about-us/our-role/managing-conservation/conservation-amendment-bill</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:05:57.831Z</t>
+  </si>
+  <si>
+    <t>EMA: Conservation Amendment Bill: Managing conservation</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/about-us/our-role/managing-conservation/conservation-amendment-bill/</t>
+  </si>
+  <si>
+    <t>news/events/national-events/national-wild-goat-hunting-competition.report.json</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/f7be0a20cbaa45f1b78b2d52b6d366b2/national-wild-goat-competition-2026-1920.jpg -&gt; /content/dam/nzdoc/heros/national-wild-goat-competition-2026-1920.jpg</t>
+  </si>
+  <si>
+    <t>news/events/national-events/national-wild-goat-hunting-competition</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:14:05.267Z</t>
+  </si>
+  <si>
+    <t>EMA: National Wild Goat Hunting Competition 2026</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/news/events/national-events/national-wild-goat-hunting-competition/</t>
+  </si>
+  <si>
+    <t>news/media-releases/2026-media-releases/4wd-group-plants-native-trees-to-fix-damage.report.json</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/6bd3432a1fe849b3848184b73ccc07b6/planting-with-damage-in-background1920.jpg -&gt; /content/dam/nzdoc/heros/planting-with-damage-in-background1920.jpg</t>
+  </si>
+  <si>
+    <t>news/media-releases/2026-media-releases/4wd-group-plants-native-trees-to-fix-damage</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:06:25.267Z</t>
+  </si>
+  <si>
+    <t>EMA: 4WD group plants native trees to fix damage</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/news/media-releases/2026-media-releases/4wd-group-plants-native-trees-to-fix-damage/</t>
+  </si>
+  <si>
+    <t>news/media-releases/2026-media-releases/funding-boost-for-bird-flu-surveillance.report.json</t>
+  </si>
+  <si>
+    <t>news/media-releases/2026-media-releases/funding-boost-for-bird-flu-surveillance</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:06:12.822Z</t>
+  </si>
+  <si>
+    <t>EMA: Funding boost for bird flu surveillance: Media release 24 September 2026</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/news/media-releases/2026-media-releases/funding-boost-for-bird-flu-surveillance/</t>
+  </si>
+  <si>
+    <t>news/media-releases/2026-media-releases/government-invests-in-cleaning-up-contaminated-crown-land.report.json</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/0e132745d3954aa8848ca8a263fb8400/puhipuhi-1920.jpg -&gt; /content/dam/nzdoc/heros/puhipuhi-1920.jpg</t>
+  </si>
+  <si>
+    <t>news/media-releases/2026-media-releases/government-invests-in-cleaning-up-contaminated-crown-land</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:06:18.888Z</t>
+  </si>
+  <si>
+    <t>EMA: Government invests in cleaning up contaminated Crown land: Media release 23 September 2026</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/news/media-releases/2026-media-releases/government-invests-in-cleaning-up-contaminated-crown-land/</t>
+  </si>
+  <si>
+    <t>news/media-releases/2026-media-releases/toxoplasmosis-confirmed-as-cause-of-death-of-pregnant-hectors-dolphin.report.json</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/adba4374a3f54a75af306e54efe345f5/hectors-deceased-1920.jpg -&gt; /content/dam/nzdoc/heros/hectors-deceased-1920.jpg</t>
+  </si>
+  <si>
+    <t>news/media-releases/2026-media-releases/toxoplasmosis-confirmed-as-cause-of-death-of-pregnant-hectors-dolphin</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:06:32.869Z</t>
+  </si>
+  <si>
+    <t>EMA: Toxoplasmosis confirmed as cause of death of pregnant Hector’s dolphin: Media release 22 September 2026</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/news/media-releases/2026-media-releases/toxoplasmosis-confirmed-as-cause-of-death-of-pregnant-hectors-dolphin/</t>
+  </si>
+  <si>
+    <t>parks-and-recreation/things-to-do/fishing/whitebaiting.report.json</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/7844f904c74341bf9c8ddaefc05726ce/whitebaiter-in-westland-hero.jpg -&gt; /content/dam/nzdoc/heros/whitebaiter-in-westland-hero.jpg</t>
+  </si>
+  <si>
+    <t>parks-and-recreation/things-to-do/fishing/whitebaiting</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:05:51.019Z</t>
+  </si>
+  <si>
+    <t>EMA: Whitebaiting: Things to do</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/parks-and-recreation/things-to-do/fishing/whitebaiting/</t>
   </si>
 </sst>
 </file>
@@ -459,20 +612,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="33" customWidth="1"/>
-    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="3" max="6" width="50" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="11" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,41 +654,327 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,9 +19,6 @@
     <t>blocks</t>
   </si>
   <si>
-    <t>contentListMore</t>
-  </si>
-  <si>
     <t>damImages</t>
   </si>
   <si>
@@ -52,9 +49,6 @@
     <t>["hero","cards","columns","feedback"]</t>
   </si>
   <si>
-    <t>Featured: https://www.doc.govt.nz/footer-links/new-on-the-site/; Media releases: https://www.doc.govt.nz/news/media-releases/2026-media-releases/</t>
-  </si>
-  <si>
     <t>https://www.doc.govt.nz/thumbs/hero/contentassets/9b48a55da5974906b6d65a89fb9d5d06/kura-tawhiti-hero.jpg -&gt; /content/dam/nzdoc/heros/kura-tawhiti-hero.jpg; https://www.doc.govt.nz/thumbs/gallery/contentassets/a8cf8502518043808b916575ca1bb512/denniston-hero.jpg -&gt; /content/dam/nzdoc/heros/denniston-hero.jpg; https://i0.wp.com/blog.doc.govt.nz/wp-content/uploads/2026/09/black-robin-invertebrate-leon-everett-1-e1788825954346.jpg?w=200 -&gt; /content/dam/nzdoc/blogs/2026/black-robin-invertebrate-leon-everett-1-e1788825954346.jpg</t>
   </si>
   <si>
@@ -70,7 +64,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-28T03:19:20.863Z</t>
+    <t>2026-09-28T03:31:15.762Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
@@ -612,18 +606,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="6" width="50" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
-    <col min="10" max="11" width="50" customWidth="1"/>
+    <col min="3" max="5" width="50" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -654,327 +648,297 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
         <v>21</v>
       </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G8" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
+      <c r="H8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="G10" t="s">
         <v>24</v>
       </c>
-      <c r="F7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" t="s">
-        <v>63</v>
-      </c>
-      <c r="K9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="H10" t="s">
         <v>66</v>
       </c>
-      <c r="F10" t="s">
+      <c r="I10" t="s">
         <v>67</v>
       </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>68</v>
-      </c>
-      <c r="J10" t="s">
-        <v>69</v>
-      </c>
-      <c r="K10" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
   <si>
     <t>_reportFile</t>
   </si>
@@ -31,6 +31,9 @@
     <t>status</t>
   </si>
   <si>
+    <t>subtitle</t>
+  </si>
+  <si>
     <t>template</t>
   </si>
   <si>
@@ -64,7 +67,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-28T03:31:15.762Z</t>
+    <t>2026-09-29T03:18:55.011Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
@@ -76,73 +79,88 @@
     <t>news/issues/bird-flu-updates.report.json</t>
   </si>
   <si>
+    <t>["breadcrumb","hero","feedback"]</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/thumbs/hero/globalassets/images/nature/native-animals/birds/brown-skua/brown-skua-1920.jpg -&gt; /content/dam/nzdoc/heros/brown-skua-1920.jpg</t>
+  </si>
+  <si>
+    <t>news/issues/bird-flu-updates</t>
+  </si>
+  <si>
+    <t>H5 bird flu (H5N1 avian influenza) has been detected in New Zealand.</t>
+  </si>
+  <si>
+    <t>article-hero</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:53:56.352Z</t>
+  </si>
+  <si>
+    <t>EMA: Bird flu updates: Issues</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/news/issues/bird-flu-updates/</t>
+  </si>
+  <si>
+    <t>about-us/our-role/managing-conservation/conservation-amendment-bill.report.json</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/59e382809add463ea8fa893707db334d/whakatane-hero.jpg -&gt; /content/dam/nzdoc/heros/whakatane-hero.jpg</t>
+  </si>
+  <si>
+    <t>about-us/our-role/managing-conservation/conservation-amendment-bill</t>
+  </si>
+  <si>
+    <t>The Conservation Amendment Bill aims to modernise the way conservation land is managed, support economic growth, and deliver stronger conservation outcomes.</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:54:09.373Z</t>
+  </si>
+  <si>
+    <t>EMA: Conservation Amendment Bill: Managing conservation</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/about-us/our-role/managing-conservation/conservation-amendment-bill/</t>
+  </si>
+  <si>
+    <t>news/events/national-events/national-wild-goat-hunting-competition.report.json</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/f7be0a20cbaa45f1b78b2d52b6d366b2/national-wild-goat-competition-2026-1920.jpg -&gt; /content/dam/nzdoc/heros/national-wild-goat-competition-2026-1920.jpg</t>
+  </si>
+  <si>
+    <t>news/events/national-events/national-wild-goat-hunting-competition</t>
+  </si>
+  <si>
+    <t>Turn your wild goat hunt – whether it's your first or your fourth, solo or with mates – into meaningful action. Help reduce pressure on New Zealand's landscapes and go in the draw to win.</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:54:14.897Z</t>
+  </si>
+  <si>
+    <t>EMA: National Wild Goat Hunting Competition 2026</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/news/events/national-events/national-wild-goat-hunting-competition/</t>
+  </si>
+  <si>
+    <t>news/media-releases/2026-media-releases/4wd-group-plants-native-trees-to-fix-damage.report.json</t>
+  </si>
+  <si>
     <t>["breadcrumb","hero"]</t>
   </si>
   <si>
-    <t>https://www.doc.govt.nz/thumbs/hero/globalassets/images/nature/native-animals/birds/brown-skua/brown-skua-1920.jpg -&gt; /content/dam/nzdoc/heros/brown-skua-1920.jpg</t>
-  </si>
-  <si>
-    <t>news/issues/bird-flu-updates</t>
-  </si>
-  <si>
-    <t>article-hero</t>
-  </si>
-  <si>
-    <t>2026-09-28T03:05:43.233Z</t>
-  </si>
-  <si>
-    <t>EMA: Bird flu updates: Issues</t>
-  </si>
-  <si>
-    <t>https://www.doc.govt.nz/news/issues/bird-flu-updates/</t>
-  </si>
-  <si>
-    <t>about-us/our-role/managing-conservation/conservation-amendment-bill.report.json</t>
-  </si>
-  <si>
-    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/59e382809add463ea8fa893707db334d/whakatane-hero.jpg -&gt; /content/dam/nzdoc/heros/whakatane-hero.jpg</t>
-  </si>
-  <si>
-    <t>about-us/our-role/managing-conservation/conservation-amendment-bill</t>
-  </si>
-  <si>
-    <t>2026-09-28T03:05:57.831Z</t>
-  </si>
-  <si>
-    <t>EMA: Conservation Amendment Bill: Managing conservation</t>
-  </si>
-  <si>
-    <t>https://www.doc.govt.nz/about-us/our-role/managing-conservation/conservation-amendment-bill/</t>
-  </si>
-  <si>
-    <t>news/events/national-events/national-wild-goat-hunting-competition.report.json</t>
-  </si>
-  <si>
-    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/f7be0a20cbaa45f1b78b2d52b6d366b2/national-wild-goat-competition-2026-1920.jpg -&gt; /content/dam/nzdoc/heros/national-wild-goat-competition-2026-1920.jpg</t>
-  </si>
-  <si>
-    <t>news/events/national-events/national-wild-goat-hunting-competition</t>
-  </si>
-  <si>
-    <t>2026-09-28T03:14:05.267Z</t>
-  </si>
-  <si>
-    <t>EMA: National Wild Goat Hunting Competition 2026</t>
-  </si>
-  <si>
-    <t>https://www.doc.govt.nz/news/events/national-events/national-wild-goat-hunting-competition/</t>
-  </si>
-  <si>
-    <t>news/media-releases/2026-media-releases/4wd-group-plants-native-trees-to-fix-damage.report.json</t>
-  </si>
-  <si>
     <t>https://www.doc.govt.nz/thumbs/hero/contentassets/6bd3432a1fe849b3848184b73ccc07b6/planting-with-damage-in-background1920.jpg -&gt; /content/dam/nzdoc/heros/planting-with-damage-in-background1920.jpg</t>
   </si>
   <si>
     <t>news/media-releases/2026-media-releases/4wd-group-plants-native-trees-to-fix-damage</t>
   </si>
   <si>
-    <t>2026-09-28T03:06:25.267Z</t>
+    <t>A four-wheel drive (4WD) club has joined forces with the Department of Conservation to fund and plant native shrubs and trees to help cover damage done by vehicles.</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:54:33.072Z</t>
   </si>
   <si>
     <t>EMA: 4WD group plants native trees to fix damage</t>
@@ -157,7 +175,10 @@
     <t>news/media-releases/2026-media-releases/funding-boost-for-bird-flu-surveillance</t>
   </si>
   <si>
-    <t>2026-09-28T03:06:12.822Z</t>
+    <t>The government is boosting support for wildlife care facilities because of their key role in New Zealand’s bird flu surveillance and response, Conservation Minister Tama Potaka and Biosecurity Minister Andrew Hoggard say.</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:54:21.591Z</t>
   </si>
   <si>
     <t>EMA: Funding boost for bird flu surveillance: Media release 24 September 2026</t>
@@ -175,7 +196,10 @@
     <t>news/media-releases/2026-media-releases/government-invests-in-cleaning-up-contaminated-crown-land</t>
   </si>
   <si>
-    <t>2026-09-28T03:06:18.888Z</t>
+    <t>The Government is taking a practical step to address contaminated sites on Crown-owned land.</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:54:27.239Z</t>
   </si>
   <si>
     <t>EMA: Government invests in cleaning up contaminated Crown land: Media release 23 September 2026</t>
@@ -193,7 +217,10 @@
     <t>news/media-releases/2026-media-releases/toxoplasmosis-confirmed-as-cause-of-death-of-pregnant-hectors-dolphin</t>
   </si>
   <si>
-    <t>2026-09-28T03:06:32.869Z</t>
+    <t>DOC has confirmed toxoplasmosis was the cause of death of a pregnant Hector’s dolphin found at Invercargill’s Oreti Beach last month.</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:54:38.824Z</t>
   </si>
   <si>
     <t>EMA: Toxoplasmosis confirmed as cause of death of pregnant Hector’s dolphin: Media release 22 September 2026</t>
@@ -211,13 +238,40 @@
     <t>parks-and-recreation/things-to-do/fishing/whitebaiting</t>
   </si>
   <si>
-    <t>2026-09-28T03:05:51.019Z</t>
+    <t>The whitebait fishing season is open. Find out when, where and how to fish for whitebait in New Zealand and the Chatham Islands.</t>
+  </si>
+  <si>
+    <t>2026-09-28T03:54:02.394Z</t>
   </si>
   <si>
     <t>EMA: Whitebaiting: Things to do</t>
   </si>
   <si>
     <t>https://www.doc.govt.nz/parks-and-recreation/things-to-do/fishing/whitebaiting/</t>
+  </si>
+  <si>
+    <t>parks-and-recreation/things-to-do/walking-and-tramping/short-walks.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","hero","columns","feedback"]</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/thumbs/hero/contentassets/a8cf8502518043808b916575ca1bb512/denniston-hero.jpg -&gt; /content/dam/nzdoc/heros/denniston-hero.jpg</t>
+  </si>
+  <si>
+    <t>parks-and-recreation/things-to-do/walking-and-tramping/short-walks</t>
+  </si>
+  <si>
+    <t>Discover some of our best short walks. They’re easy to get to and great for families – there’s something for everyone.</t>
+  </si>
+  <si>
+    <t>2026-09-29T03:02:53.982Z</t>
+  </si>
+  <si>
+    <t>EMA: Short Walks: Walking and tramping</t>
+  </si>
+  <si>
+    <t>https://www.doc.govt.nz/parks-and-recreation/things-to-do/walking-and-tramping/short-walks/</t>
   </si>
 </sst>
 </file>
@@ -606,18 +660,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
     <col min="3" max="5" width="50" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="10" width="50" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="11" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -648,28 +703,31 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
         <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -680,265 +738,327 @@
       <c r="J2" t="s">
         <v>19</v>
       </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" t="s">
         <v>26</v>
       </c>
-      <c r="J3" t="s">
-        <v>27</v>
+      <c r="I7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" t="s">
-        <v>33</v>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" t="s">
-        <v>39</v>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" t="s">
-        <v>45</v>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" t="s">
-        <v>68</v>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
   <si>
     <t>_reportFile</t>
   </si>
@@ -67,7 +67,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-29T03:18:55.011Z</t>
+    <t>2026-09-29T04:46:35.577Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
@@ -94,7 +94,7 @@
     <t>article-hero</t>
   </si>
   <si>
-    <t>2026-09-28T03:53:56.352Z</t>
+    <t>2026-09-29T03:19:03.033Z</t>
   </si>
   <si>
     <t>EMA: Bird flu updates: Issues</t>
@@ -115,7 +115,7 @@
     <t>The Conservation Amendment Bill aims to modernise the way conservation land is managed, support economic growth, and deliver stronger conservation outcomes.</t>
   </si>
   <si>
-    <t>2026-09-28T03:54:09.373Z</t>
+    <t>2026-09-29T03:19:16.392Z</t>
   </si>
   <si>
     <t>EMA: Conservation Amendment Bill: Managing conservation</t>
@@ -127,6 +127,9 @@
     <t>news/events/national-events/national-wild-goat-hunting-competition.report.json</t>
   </si>
   <si>
+    <t>["breadcrumb","hero","accordion","feedback"]</t>
+  </si>
+  <si>
     <t>https://www.doc.govt.nz/thumbs/hero/contentassets/f7be0a20cbaa45f1b78b2d52b6d366b2/national-wild-goat-competition-2026-1920.jpg -&gt; /content/dam/nzdoc/heros/national-wild-goat-competition-2026-1920.jpg</t>
   </si>
   <si>
@@ -136,7 +139,10 @@
     <t>Turn your wild goat hunt – whether it's your first or your fourth, solo or with mates – into meaningful action. Help reduce pressure on New Zealand's landscapes and go in the draw to win.</t>
   </si>
   <si>
-    <t>2026-09-28T03:54:14.897Z</t>
+    <t>article-full</t>
+  </si>
+  <si>
+    <t>2026-09-29T03:51:05.157Z</t>
   </si>
   <si>
     <t>EMA: National Wild Goat Hunting Competition 2026</t>
@@ -160,7 +166,7 @@
     <t>A four-wheel drive (4WD) club has joined forces with the Department of Conservation to fund and plant native shrubs and trees to help cover damage done by vehicles.</t>
   </si>
   <si>
-    <t>2026-09-28T03:54:33.072Z</t>
+    <t>2026-09-29T03:19:42.140Z</t>
   </si>
   <si>
     <t>EMA: 4WD group plants native trees to fix damage</t>
@@ -178,7 +184,7 @@
     <t>The government is boosting support for wildlife care facilities because of their key role in New Zealand’s bird flu surveillance and response, Conservation Minister Tama Potaka and Biosecurity Minister Andrew Hoggard say.</t>
   </si>
   <si>
-    <t>2026-09-28T03:54:21.591Z</t>
+    <t>2026-09-29T03:19:30.980Z</t>
   </si>
   <si>
     <t>EMA: Funding boost for bird flu surveillance: Media release 24 September 2026</t>
@@ -199,7 +205,7 @@
     <t>The Government is taking a practical step to address contaminated sites on Crown-owned land.</t>
   </si>
   <si>
-    <t>2026-09-28T03:54:27.239Z</t>
+    <t>2026-09-29T03:19:36.448Z</t>
   </si>
   <si>
     <t>EMA: Government invests in cleaning up contaminated Crown land: Media release 23 September 2026</t>
@@ -220,7 +226,7 @@
     <t>DOC has confirmed toxoplasmosis was the cause of death of a pregnant Hector’s dolphin found at Invercargill’s Oreti Beach last month.</t>
   </si>
   <si>
-    <t>2026-09-28T03:54:38.824Z</t>
+    <t>2026-09-29T03:19:49.230Z</t>
   </si>
   <si>
     <t>EMA: Toxoplasmosis confirmed as cause of death of pregnant Hector’s dolphin: Media release 22 September 2026</t>
@@ -241,7 +247,7 @@
     <t>The whitebait fishing season is open. Find out when, where and how to fish for whitebait in New Zealand and the Chatham Islands.</t>
   </si>
   <si>
-    <t>2026-09-28T03:54:02.394Z</t>
+    <t>2026-09-29T03:19:09.164Z</t>
   </si>
   <si>
     <t>EMA: Whitebaiting: Things to do</t>
@@ -265,7 +271,7 @@
     <t>Discover some of our best short walks. They’re easy to get to and great for families – there’s something for everyone.</t>
   </si>
   <si>
-    <t>2026-09-29T03:02:53.982Z</t>
+    <t>2026-09-29T03:20:14.137Z</t>
   </si>
   <si>
     <t>EMA: Short Walks: Walking and tramping</t>
@@ -664,7 +670,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="5" width="50" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
@@ -817,77 +823,77 @@
         <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" t="s">
         <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -896,100 +902,100 @@
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H7" t="s">
         <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H8" t="s">
         <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H9" t="s">
         <v>26</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
@@ -998,63 +1004,63 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s">
         <v>26</v>
       </c>
       <c r="I10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
         <v>26</v>
       </c>
       <c r="I11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -67,7 +67,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-29T04:46:35.577Z</t>
+    <t>2026-09-29T05:48:27.130Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
@@ -94,7 +94,7 @@
     <t>article-hero</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:03.033Z</t>
+    <t>2026-09-29T05:43:41.352Z</t>
   </si>
   <si>
     <t>EMA: Bird flu updates: Issues</t>
@@ -115,7 +115,7 @@
     <t>The Conservation Amendment Bill aims to modernise the way conservation land is managed, support economic growth, and deliver stronger conservation outcomes.</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:16.392Z</t>
+    <t>2026-09-29T05:43:58.392Z</t>
   </si>
   <si>
     <t>EMA: Conservation Amendment Bill: Managing conservation</t>
@@ -142,7 +142,7 @@
     <t>article-full</t>
   </si>
   <si>
-    <t>2026-09-29T03:51:05.157Z</t>
+    <t>2026-09-29T05:45:24.696Z</t>
   </si>
   <si>
     <t>EMA: National Wild Goat Hunting Competition 2026</t>
@@ -166,7 +166,7 @@
     <t>A four-wheel drive (4WD) club has joined forces with the Department of Conservation to fund and plant native shrubs and trees to help cover damage done by vehicles.</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:42.140Z</t>
+    <t>2026-09-29T05:44:15.271Z</t>
   </si>
   <si>
     <t>EMA: 4WD group plants native trees to fix damage</t>
@@ -184,7 +184,7 @@
     <t>The government is boosting support for wildlife care facilities because of their key role in New Zealand’s bird flu surveillance and response, Conservation Minister Tama Potaka and Biosecurity Minister Andrew Hoggard say.</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:30.980Z</t>
+    <t>2026-09-29T05:44:02.956Z</t>
   </si>
   <si>
     <t>EMA: Funding boost for bird flu surveillance: Media release 24 September 2026</t>
@@ -205,7 +205,7 @@
     <t>The Government is taking a practical step to address contaminated sites on Crown-owned land.</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:36.448Z</t>
+    <t>2026-09-29T05:44:08.382Z</t>
   </si>
   <si>
     <t>EMA: Government invests in cleaning up contaminated Crown land: Media release 23 September 2026</t>
@@ -226,7 +226,7 @@
     <t>DOC has confirmed toxoplasmosis was the cause of death of a pregnant Hector’s dolphin found at Invercargill’s Oreti Beach last month.</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:49.230Z</t>
+    <t>2026-09-29T05:44:21.746Z</t>
   </si>
   <si>
     <t>EMA: Toxoplasmosis confirmed as cause of death of pregnant Hector’s dolphin: Media release 22 September 2026</t>
@@ -247,7 +247,7 @@
     <t>The whitebait fishing season is open. Find out when, where and how to fish for whitebait in New Zealand and the Chatham Islands.</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:09.164Z</t>
+    <t>2026-09-29T05:43:49.745Z</t>
   </si>
   <si>
     <t>EMA: Whitebaiting: Things to do</t>
@@ -271,7 +271,7 @@
     <t>Discover some of our best short walks. They’re easy to get to and great for families – there’s something for everyone.</t>
   </si>
   <si>
-    <t>2026-09-29T03:20:14.137Z</t>
+    <t>2026-09-29T05:45:13.395Z</t>
   </si>
   <si>
     <t>EMA: Short Walks: Walking and tramping</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -67,7 +67,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-29T05:48:27.130Z</t>
+    <t>2026-09-29T06:18:51.603Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
@@ -94,7 +94,7 @@
     <t>article-hero</t>
   </si>
   <si>
-    <t>2026-09-29T05:43:41.352Z</t>
+    <t>2026-09-29T05:48:36.788Z</t>
   </si>
   <si>
     <t>EMA: Bird flu updates: Issues</t>
@@ -115,7 +115,7 @@
     <t>The Conservation Amendment Bill aims to modernise the way conservation land is managed, support economic growth, and deliver stronger conservation outcomes.</t>
   </si>
   <si>
-    <t>2026-09-29T05:43:58.392Z</t>
+    <t>2026-09-29T05:48:49.691Z</t>
   </si>
   <si>
     <t>EMA: Conservation Amendment Bill: Managing conservation</t>
@@ -142,7 +142,7 @@
     <t>article-full</t>
   </si>
   <si>
-    <t>2026-09-29T05:45:24.696Z</t>
+    <t>2026-09-29T05:50:12.484Z</t>
   </si>
   <si>
     <t>EMA: National Wild Goat Hunting Competition 2026</t>
@@ -166,7 +166,7 @@
     <t>A four-wheel drive (4WD) club has joined forces with the Department of Conservation to fund and plant native shrubs and trees to help cover damage done by vehicles.</t>
   </si>
   <si>
-    <t>2026-09-29T05:44:15.271Z</t>
+    <t>2026-09-29T05:49:08.031Z</t>
   </si>
   <si>
     <t>EMA: 4WD group plants native trees to fix damage</t>
@@ -184,7 +184,7 @@
     <t>The government is boosting support for wildlife care facilities because of their key role in New Zealand’s bird flu surveillance and response, Conservation Minister Tama Potaka and Biosecurity Minister Andrew Hoggard say.</t>
   </si>
   <si>
-    <t>2026-09-29T05:44:02.956Z</t>
+    <t>2026-09-29T05:48:56.720Z</t>
   </si>
   <si>
     <t>EMA: Funding boost for bird flu surveillance: Media release 24 September 2026</t>
@@ -205,7 +205,7 @@
     <t>The Government is taking a practical step to address contaminated sites on Crown-owned land.</t>
   </si>
   <si>
-    <t>2026-09-29T05:44:08.382Z</t>
+    <t>2026-09-29T05:49:02.558Z</t>
   </si>
   <si>
     <t>EMA: Government invests in cleaning up contaminated Crown land: Media release 23 September 2026</t>
@@ -226,7 +226,7 @@
     <t>DOC has confirmed toxoplasmosis was the cause of death of a pregnant Hector’s dolphin found at Invercargill’s Oreti Beach last month.</t>
   </si>
   <si>
-    <t>2026-09-29T05:44:21.746Z</t>
+    <t>2026-09-29T05:49:15.737Z</t>
   </si>
   <si>
     <t>EMA: Toxoplasmosis confirmed as cause of death of pregnant Hector’s dolphin: Media release 22 September 2026</t>
@@ -247,7 +247,7 @@
     <t>The whitebait fishing season is open. Find out when, where and how to fish for whitebait in New Zealand and the Chatham Islands.</t>
   </si>
   <si>
-    <t>2026-09-29T05:43:49.745Z</t>
+    <t>2026-09-29T05:48:42.473Z</t>
   </si>
   <si>
     <t>EMA: Whitebaiting: Things to do</t>
@@ -271,7 +271,7 @@
     <t>Discover some of our best short walks. They’re easy to get to and great for families – there’s something for everyone.</t>
   </si>
   <si>
-    <t>2026-09-29T05:45:13.395Z</t>
+    <t>2026-09-29T05:50:00.592Z</t>
   </si>
   <si>
     <t>EMA: Short Walks: Walking and tramping</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -67,7 +67,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-29T06:18:51.603Z</t>
+    <t>2026-09-29T06:45:35.294Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
@@ -94,7 +94,7 @@
     <t>article-hero</t>
   </si>
   <si>
-    <t>2026-09-29T05:48:36.788Z</t>
+    <t>2026-09-29T06:19:01.849Z</t>
   </si>
   <si>
     <t>EMA: Bird flu updates: Issues</t>
@@ -115,7 +115,7 @@
     <t>The Conservation Amendment Bill aims to modernise the way conservation land is managed, support economic growth, and deliver stronger conservation outcomes.</t>
   </si>
   <si>
-    <t>2026-09-29T05:48:49.691Z</t>
+    <t>2026-09-29T06:19:15.244Z</t>
   </si>
   <si>
     <t>EMA: Conservation Amendment Bill: Managing conservation</t>
@@ -142,7 +142,7 @@
     <t>article-full</t>
   </si>
   <si>
-    <t>2026-09-29T05:50:12.484Z</t>
+    <t>2026-09-29T06:20:38.591Z</t>
   </si>
   <si>
     <t>EMA: National Wild Goat Hunting Competition 2026</t>
@@ -166,7 +166,7 @@
     <t>A four-wheel drive (4WD) club has joined forces with the Department of Conservation to fund and plant native shrubs and trees to help cover damage done by vehicles.</t>
   </si>
   <si>
-    <t>2026-09-29T05:49:08.031Z</t>
+    <t>2026-09-29T06:19:34.740Z</t>
   </si>
   <si>
     <t>EMA: 4WD group plants native trees to fix damage</t>
@@ -184,7 +184,7 @@
     <t>The government is boosting support for wildlife care facilities because of their key role in New Zealand’s bird flu surveillance and response, Conservation Minister Tama Potaka and Biosecurity Minister Andrew Hoggard say.</t>
   </si>
   <si>
-    <t>2026-09-29T05:48:56.720Z</t>
+    <t>2026-09-29T06:19:22.039Z</t>
   </si>
   <si>
     <t>EMA: Funding boost for bird flu surveillance: Media release 24 September 2026</t>
@@ -205,7 +205,7 @@
     <t>The Government is taking a practical step to address contaminated sites on Crown-owned land.</t>
   </si>
   <si>
-    <t>2026-09-29T05:49:02.558Z</t>
+    <t>2026-09-29T06:19:28.613Z</t>
   </si>
   <si>
     <t>EMA: Government invests in cleaning up contaminated Crown land: Media release 23 September 2026</t>
@@ -226,7 +226,7 @@
     <t>DOC has confirmed toxoplasmosis was the cause of death of a pregnant Hector’s dolphin found at Invercargill’s Oreti Beach last month.</t>
   </si>
   <si>
-    <t>2026-09-29T05:49:15.737Z</t>
+    <t>2026-09-29T06:19:42.918Z</t>
   </si>
   <si>
     <t>EMA: Toxoplasmosis confirmed as cause of death of pregnant Hector’s dolphin: Media release 22 September 2026</t>
@@ -247,7 +247,7 @@
     <t>The whitebait fishing season is open. Find out when, where and how to fish for whitebait in New Zealand and the Chatham Islands.</t>
   </si>
   <si>
-    <t>2026-09-29T05:48:42.473Z</t>
+    <t>2026-09-29T06:19:09.443Z</t>
   </si>
   <si>
     <t>EMA: Whitebaiting: Things to do</t>
@@ -271,7 +271,7 @@
     <t>Discover some of our best short walks. They’re easy to get to and great for families – there’s something for everyone.</t>
   </si>
   <si>
-    <t>2026-09-29T05:50:00.592Z</t>
+    <t>2026-09-29T06:20:27.992Z</t>
   </si>
   <si>
     <t>EMA: Short Walks: Walking and tramping</t>
